--- a/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="275">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,7 +94,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -489,7 +489,7 @@
     <t>FRCDAMaterialPharm.asSpecializedKind.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">id
 </t>
   </si>
   <si>
@@ -500,6 +500,10 @@
   </si>
   <si>
     <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>FRCDAMaterialPharm.asSpecializedKind.extension</t>
@@ -516,7 +520,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -552,11 +556,11 @@
     <t>Extensions that cannot be ignored even if unrecognized</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -3231,7 +3235,7 @@
         <v>74</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>73</v>
@@ -3242,14 +3246,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3268,16 +3272,16 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3315,19 +3319,19 @@
         <v>73</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3339,7 +3343,7 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
@@ -3347,14 +3351,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3367,25 +3371,25 @@
         <v>73</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3434,7 +3438,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3446,18 +3450,18 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3480,13 +3484,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3498,7 +3502,7 @@
         <v>73</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>73</v>
@@ -3537,7 +3541,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3557,10 +3561,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3586,10 +3590,10 @@
         <v>148</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3640,7 +3644,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3660,10 +3664,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3752,7 +3756,7 @@
         <v>74</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>73</v>
@@ -3763,14 +3767,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3789,16 +3793,16 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3836,19 +3840,19 @@
         <v>73</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -3860,7 +3864,7 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
@@ -3868,14 +3872,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3888,25 +3892,25 @@
         <v>73</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -3955,7 +3959,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -3967,18 +3971,18 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4001,13 +4005,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4058,7 +4062,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4078,10 +4082,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4107,10 +4111,10 @@
         <v>129</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4161,7 +4165,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4181,10 +4185,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4210,10 +4214,10 @@
         <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4264,7 +4268,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4284,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4313,10 +4317,10 @@
         <v>148</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4367,7 +4371,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4387,10 +4391,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4479,7 +4483,7 @@
         <v>74</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>73</v>
@@ -4490,14 +4494,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4516,16 +4520,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4563,19 +4567,19 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4587,7 +4591,7 @@
         <v>73</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -4595,14 +4599,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4615,25 +4619,25 @@
         <v>73</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>73</v>
@@ -4682,7 +4686,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -4694,18 +4698,18 @@
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4728,13 +4732,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4746,7 +4750,7 @@
         <v>73</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>73</v>
@@ -4785,7 +4789,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4805,10 +4809,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4831,13 +4835,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4888,7 +4892,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -4908,10 +4912,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4937,10 +4941,10 @@
         <v>148</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4991,7 +4995,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5011,10 +5015,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5103,7 +5107,7 @@
         <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>73</v>
@@ -5114,14 +5118,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5140,16 +5144,16 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5187,19 +5191,19 @@
         <v>73</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5211,7 +5215,7 @@
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -5219,14 +5223,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5239,25 +5243,25 @@
         <v>73</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -5306,7 +5310,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5318,18 +5322,18 @@
         <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5352,13 +5356,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5409,7 +5413,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5429,10 +5433,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5455,13 +5459,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5512,7 +5516,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5532,10 +5536,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5561,10 +5565,10 @@
         <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5615,7 +5619,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -5635,10 +5639,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5736,10 +5740,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5768,7 +5772,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5819,7 +5823,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -5839,17 +5843,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>77</v>
@@ -5871,7 +5875,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5922,7 +5926,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -5942,17 +5946,17 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>77</v>
@@ -5974,7 +5978,7 @@
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6025,7 +6029,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6045,17 +6049,17 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>77</v>
@@ -6077,7 +6081,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6128,7 +6132,7 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6148,17 +6152,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>77</v>
@@ -6180,7 +6184,7 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6231,7 +6235,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6251,10 +6255,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6277,11 +6281,11 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6332,7 +6336,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -6352,10 +6356,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6382,7 +6386,7 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6433,7 +6437,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -6453,17 +6457,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>77</v>
@@ -6481,11 +6485,11 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6536,7 +6540,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -6556,10 +6560,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6582,13 +6586,13 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6639,7 +6643,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -6659,17 +6663,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>77</v>
@@ -6687,11 +6691,11 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6742,7 +6746,7 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -6762,17 +6766,17 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>77</v>
@@ -6790,11 +6794,11 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6845,7 +6849,7 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -6865,10 +6869,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6894,10 +6898,10 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6948,7 +6952,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>

--- a/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,7 +582,7 @@
     <t>Code indiquant qu'il s'agit d'une relation vers une classe générique ou thérapeutique.</t>
   </si>
   <si>
-    <t>GRIC</t>
+    <t>GRICAWATIF</t>
   </si>
   <si>
     <t>FRCDAMaterialPharm.asSpecializedKind.generalizedMedicineClass</t>

--- a/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,7 +582,7 @@
     <t>Code indiquant qu'il s'agit d'une relation vers une classe générique ou thérapeutique.</t>
   </si>
   <si>
-    <t>GRICAWATIF</t>
+    <t>GRIC</t>
   </si>
   <si>
     <t>FRCDAMaterialPharm.asSpecializedKind.generalizedMedicineClass</t>

--- a/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-FRCDAMaterialPharm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2701" uniqueCount="322">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -460,33 +460,34 @@
     <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
-    <t>FRCDAMaterialPharm.formCode</t>
-  </si>
-  <si>
-    <t>Forme pharmaceutique</t>
-  </si>
-  <si>
-    <t>Code représentant la forme pharmaceutique du produit de santé.</t>
-  </si>
-  <si>
-    <t>FRCDAMaterialPharm.asSpecializedKind</t>
+    <t>FRCDAMaterialPharm.expirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL_TS {http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS|2.0.3-sd}
+</t>
+  </si>
+  <si>
+    <t>Date d'expiration du produit</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Classification du produit</t>
-  </si>
-  <si>
-    <t>Relation entre le produit de santé et une classe générique ou thérapeutique.</t>
+    <t>Présentation / conditionnement</t>
+  </si>
+  <si>
+    <t>Description du conditionnement du produit de santé.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>FRCDAMaterialPharm.asSpecializedKind.id</t>
+    <t>FRCDAMaterialPharm.asContent.id</t>
   </si>
   <si>
     <t xml:space="preserve">id
@@ -506,7 +507,7 @@
 </t>
   </si>
   <si>
-    <t>FRCDAMaterialPharm.asSpecializedKind.extension</t>
+    <t>FRCDAMaterialPharm.asContent.extension</t>
   </si>
   <si>
     <t>extensions
@@ -543,7 +544,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>FRCDAMaterialPharm.asSpecializedKind.modifierExtension</t>
+    <t>FRCDAMaterialPharm.asContent.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -569,11 +570,153 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>FRCDAMaterialPharm.asSpecializedKind.classCode</t>
+    <t>FRCDAMaterialPharm.asContent.classCode</t>
   </si>
   <si>
     <t xml:space="preserve">code
 </t>
+  </si>
+  <si>
+    <t>Classe de la relation contenu</t>
+  </si>
+  <si>
+    <t>CONT</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>Conditionnement primaire</t>
+  </si>
+  <si>
+    <t>Description du conditionnement primaire du produit.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.id</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.extension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.modifierExtension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.classCode</t>
+  </si>
+  <si>
+    <t>Classe du conditionnement</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.determinerCode</t>
+  </si>
+  <si>
+    <t>Type du conditionnement</t>
+  </si>
+  <si>
+    <t>INSTANCE</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.code</t>
+  </si>
+  <si>
+    <t>Code du produit de santé prescrit</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.name</t>
+  </si>
+  <si>
+    <t>Nom de marque du conditionnement</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.formCode</t>
+  </si>
+  <si>
+    <t>Conditionnement</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PQ
+</t>
+  </si>
+  <si>
+    <t>Capacité du conditionnement primaire</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent</t>
+  </si>
+  <si>
+    <t>Conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.id</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.extension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.modifierExtension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.id</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.extension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.modifierExtension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.classCode</t>
+  </si>
+  <si>
+    <t>Classe du conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.determinerCode</t>
+  </si>
+  <si>
+    <t>Type du conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asContent.containerPackagedMedicine.asSuperContent.containerPackagedMedicine.capacityQuantity</t>
+  </si>
+  <si>
+    <t>Capacité du conditionnement supérieur</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.formCode</t>
+  </si>
+  <si>
+    <t>Forme pharmaceutique</t>
+  </si>
+  <si>
+    <t>Code représentant la forme pharmaceutique du produit de santé.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asSpecializedKind</t>
+  </si>
+  <si>
+    <t>Classification du produit</t>
+  </si>
+  <si>
+    <t>Relation entre le produit de santé et une classe générique ou thérapeutique.</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asSpecializedKind.id</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asSpecializedKind.extension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asSpecializedKind.modifierExtension</t>
+  </si>
+  <si>
+    <t>FRCDAMaterialPharm.asSpecializedKind.classCode</t>
   </si>
   <si>
     <t>Classe de la relation</t>
@@ -1169,11 +1312,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="67.98046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="67.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="99.3203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="99.3203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
@@ -1203,7 +1346,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="61.65625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="98.5" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2848,7 +2991,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2963,10 +3106,10 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>146</v>
@@ -3490,7 +3633,7 @@
         <v>179</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3502,7 +3645,7 @@
         <v>73</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>73</v>
@@ -3561,10 +3704,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3590,10 +3733,10 @@
         <v>148</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3644,7 +3787,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3664,10 +3807,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3767,10 +3910,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3872,10 +4015,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3979,10 +4122,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4008,10 +4151,10 @@
         <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4023,7 +4166,7 @@
         <v>73</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>73</v>
@@ -4062,7 +4205,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4082,10 +4225,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4108,13 +4251,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4126,7 +4269,7 @@
         <v>73</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>73</v>
@@ -4165,7 +4308,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4185,10 +4328,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4211,13 +4354,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4268,7 +4411,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4288,10 +4431,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4302,7 +4445,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4314,13 +4457,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4371,19 +4514,19 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>73</v>
@@ -4391,10 +4534,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4417,13 +4560,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4474,7 +4617,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4483,32 +4626,32 @@
         <v>74</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4520,17 +4663,15 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>73</v>
@@ -4567,78 +4708,74 @@
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
@@ -4686,22 +4823,22 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35">
@@ -4717,7 +4854,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>74</v>
@@ -4732,13 +4869,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4750,7 +4887,7 @@
         <v>73</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>73</v>
@@ -4789,41 +4926,41 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -4835,15 +4972,17 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -4880,74 +5019,78 @@
         <v>73</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>73</v>
       </c>
@@ -4995,30 +5138,30 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5026,7 +5169,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>74</v>
@@ -5041,13 +5184,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5098,41 +5241,41 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -5144,17 +5287,15 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5191,31 +5332,31 @@
         <v>73</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -5223,14 +5364,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5243,26 +5384,24 @@
         <v>73</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>160</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
       </c>
@@ -5298,19 +5437,19 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5325,47 +5464,51 @@
         <v>168</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>73</v>
       </c>
@@ -5374,7 +5517,7 @@
         <v>73</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>73</v>
@@ -5413,30 +5556,30 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5462,10 +5605,10 @@
         <v>178</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5477,7 +5620,7 @@
         <v>73</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>73</v>
@@ -5516,7 +5659,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5536,10 +5679,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5547,7 +5690,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>74</v>
@@ -5562,13 +5705,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5580,7 +5723,7 @@
         <v>73</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>73</v>
@@ -5619,10 +5762,10 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>74</v>
@@ -5639,20 +5782,18 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="E44" t="s" s="2">
-        <v>81</v>
-      </c>
+      <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>74</v>
@@ -5667,11 +5808,13 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="M44" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5698,11 +5841,13 @@
         <v>73</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>73</v>
@@ -5720,10 +5865,10 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>74</v>
@@ -5740,18 +5885,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="E45" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
@@ -5768,11 +5911,13 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L45" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="M45" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5823,7 +5968,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -5843,18 +5988,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="E46" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
@@ -5871,11 +6014,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L46" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M46" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5926,7 +6071,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -5938,7 +6083,7 @@
         <v>73</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>73</v>
@@ -5946,18 +6091,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>77</v>
       </c>
@@ -5974,11 +6117,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L47" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="M47" t="s" s="2">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6029,7 +6174,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6038,34 +6183,32 @@
         <v>74</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
@@ -6077,13 +6220,17 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="M48" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>73</v>
@@ -6120,74 +6267,78 @@
         <v>73</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>241</v>
+        <v>167</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L49" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="M49" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>73</v>
       </c>
@@ -6235,30 +6386,30 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6266,7 +6417,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>74</v>
@@ -6281,11 +6432,13 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="M50" t="s" s="2">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6297,7 +6450,7 @@
         <v>73</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>73</v>
@@ -6336,10 +6489,10 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>74</v>
@@ -6356,10 +6509,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6367,7 +6520,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>74</v>
@@ -6382,11 +6535,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L51" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="M51" t="s" s="2">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6437,10 +6592,10 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>74</v>
@@ -6449,7 +6604,7 @@
         <v>73</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>73</v>
@@ -6457,18 +6612,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="E52" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
@@ -6485,11 +6638,13 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L52" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="M52" t="s" s="2">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6540,7 +6695,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>257</v>
+        <v>156</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -6549,32 +6704,32 @@
         <v>74</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>73</v>
@@ -6586,15 +6741,17 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>260</v>
+        <v>161</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>73</v>
@@ -6631,74 +6788,78 @@
         <v>73</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="M54" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>73</v>
       </c>
@@ -6746,7 +6907,7 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -6758,31 +6919,29 @@
         <v>73</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>268</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>73</v>
@@ -6794,11 +6953,13 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L55" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="M55" t="s" s="2">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6810,7 +6971,7 @@
         <v>73</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>73</v>
@@ -6849,13 +7010,13 @@
         <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>73</v>
@@ -6869,10 +7030,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6895,13 +7056,13 @@
         <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6952,21 +7113,2808 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK56" t="s" s="2">
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y71" s="2"/>
+      <c r="Z71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK83" t="s" s="2">
         <v>73</v>
       </c>
     </row>
